--- a/Product-Sales-Region.xlsx
+++ b/Product-Sales-Region.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E9AD780-115C-408C-B0D0-E3BF41901653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{727F7DFF-7BBB-4B71-BE4B-19B5E7B3BA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -200,27 +200,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor theme="5" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor theme="5" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -228,42 +216,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1556,13 +1517,13 @@
     <tableColumn id="3" xr3:uid="{AD59F90D-7374-4043-8D16-CB68D58F3260}" name="Product" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{D58F2729-BD2B-426C-89D7-A52251B3708D}" name="TotalPrice" dataDxfId="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F5A6C131-D083-4822-8B33-23B4DF759106}" name="Table10" displayName="Table10" ref="J5:Y8" totalsRowShown="0">
-  <autoFilter ref="J5:Y8" xr:uid="{F5A6C131-D083-4822-8B33-23B4DF759106}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F5A6C131-D083-4822-8B33-23B4DF759106}" name="Table10" displayName="Table10" ref="F3:U6" totalsRowShown="0">
+  <autoFilter ref="F3:U6" xr:uid="{F5A6C131-D083-4822-8B33-23B4DF759106}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B5F09C47-4D8D-4526-BF62-39BAD3C121D7}" name="S.No"/>
     <tableColumn id="2" xr3:uid="{9484043F-2035-4631-966A-7BC3742DDA55}" name="1"/>
@@ -1581,51 +1542,51 @@
     <tableColumn id="15" xr3:uid="{F01D0CD6-136A-43B2-AADD-EA344C9B841B}" name="14"/>
     <tableColumn id="16" xr3:uid="{A98BA8F9-29AF-4099-9278-01E05D27193D}" name="15"/>
   </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D11C189D-CFCD-450C-B457-F675B22A4590}" name="Table11" displayName="Table11" ref="B20:C25" totalsRowShown="0">
+  <autoFilter ref="B20:C25" xr:uid="{D11C189D-CFCD-450C-B457-F675B22A4590}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{FC4726B9-8C5D-4870-8847-BEAC7275480E}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{BE7C402A-E32A-4702-A7EA-9CB5D355D903}" name="VLOOKUP"/>
+  </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D11C189D-CFCD-450C-B457-F675B22A4590}" name="Table11" displayName="Table11" ref="F6:G11" totalsRowShown="0">
-  <autoFilter ref="F6:G11" xr:uid="{D11C189D-CFCD-450C-B457-F675B22A4590}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FC4726B9-8C5D-4870-8847-BEAC7275480E}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE7C402A-E32A-4702-A7EA-9CB5D355D903}" name="VLOOKUP"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9D39D826-C031-4496-815F-040D12B98004}" name="Table12" displayName="Table12" ref="K13:L19" totalsRowShown="0">
-  <autoFilter ref="K13:L19" xr:uid="{9D39D826-C031-4496-815F-040D12B98004}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{9D39D826-C031-4496-815F-040D12B98004}" name="Table12" displayName="Table12" ref="F9:G15" totalsRowShown="0">
+  <autoFilter ref="F9:G15" xr:uid="{9D39D826-C031-4496-815F-040D12B98004}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{FB27B48D-FDE5-48FC-8EE8-2BD1F94CDF4D}" name="DESCRIPTION" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{A6CB99C3-53D6-4732-AD49-43B568D55C93}" name="HLOOKUP"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9CF6BDA7-BFA2-4560-AF4A-4E7C01C775A2}" name="Table13" displayName="Table13" ref="N13:O18" totalsRowShown="0">
-  <autoFilter ref="N13:O18" xr:uid="{9CF6BDA7-BFA2-4560-AF4A-4E7C01C775A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{9CF6BDA7-BFA2-4560-AF4A-4E7C01C775A2}" name="Table13" displayName="Table13" ref="I9:J14" totalsRowShown="0">
+  <autoFilter ref="I9:J14" xr:uid="{9CF6BDA7-BFA2-4560-AF4A-4E7C01C775A2}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{92BD3078-2A00-4149-86B8-A54CEA332088}" name="PRODUCT"/>
     <tableColumn id="2" xr3:uid="{0E823187-F763-4ECA-9917-C5EBCBB27AE0}" name="MATCH"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{8FB526EE-2D38-4E37-9DEC-FC5434A4AF0D}" name="Table15" displayName="Table15" ref="Q13:R18" totalsRowShown="0">
-  <autoFilter ref="Q13:R18" xr:uid="{8FB526EE-2D38-4E37-9DEC-FC5434A4AF0D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{6E16E63C-3296-4315-9F3F-246FA9CB68E0}" name="Table1518" displayName="Table1518" ref="L9:M14" totalsRowShown="0">
+  <autoFilter ref="L9:M14" xr:uid="{6E16E63C-3296-4315-9F3F-246FA9CB68E0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{461B90D7-758D-44F6-94D8-B9F08749268B}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{04D045C4-42BF-435E-99DB-67E6E27FA493}" name="INDEX"/>
+    <tableColumn id="1" xr3:uid="{98A04B35-C3C6-4FAF-89E1-3DA152D200CA}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{FADB1CA5-B91D-43CC-A17E-42ED2883BB26}" name="INDEX"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1924,7 +1885,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
@@ -1935,7 +1896,7 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>990895.1</v>
       </c>
     </row>
@@ -1943,7 +1904,7 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>667194.74999999988</v>
       </c>
     </row>
@@ -1951,7 +1912,7 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>1727734.8499999999</v>
       </c>
     </row>
@@ -1959,7 +1920,7 @@
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>141955</v>
       </c>
     </row>
@@ -1967,7 +1928,7 @@
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>263180</v>
       </c>
     </row>
@@ -1975,7 +1936,7 @@
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="3">
         <v>427968</v>
       </c>
     </row>
@@ -1987,15 +1948,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="9.7109375" customWidth="1"/>
@@ -2004,7 +1965,7 @@
     <col min="19" max="19" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2018,7 +1979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2032,7 +1993,7 @@
         <v>229040</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2045,8 +2006,56 @@
       <c r="D3" s="1">
         <v>436186</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2059,8 +2068,56 @@
       <c r="D4" s="1">
         <v>229040</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" t="s">
+        <v>14</v>
+      </c>
+      <c r="U4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2073,56 +2130,56 @@
       <c r="D5" s="1">
         <v>427968</v>
       </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2</v>
+      </c>
       <c r="J5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="S5" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="U5" t="s">
-        <v>33</v>
-      </c>
-      <c r="V5" t="s">
-        <v>34</v>
-      </c>
-      <c r="W5" t="s">
-        <v>35</v>
-      </c>
-      <c r="X5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2136,61 +2193,55 @@
         <v>65465</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" t="s">
-        <v>20</v>
-      </c>
-      <c r="S6" t="s">
-        <v>11</v>
-      </c>
-      <c r="T6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" t="s">
-        <v>7</v>
-      </c>
-      <c r="V6" t="s">
-        <v>13</v>
-      </c>
-      <c r="W6" t="s">
-        <v>10</v>
-      </c>
-      <c r="X6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>229040</v>
+      </c>
+      <c r="H6">
+        <v>436186</v>
+      </c>
+      <c r="I6">
+        <v>229040</v>
+      </c>
+      <c r="J6">
+        <v>427968</v>
+      </c>
+      <c r="K6">
+        <v>65465</v>
+      </c>
+      <c r="L6">
+        <v>11025</v>
+      </c>
+      <c r="M6">
+        <v>84206.1</v>
+      </c>
+      <c r="N6">
+        <v>667194.74999999988</v>
+      </c>
+      <c r="O6">
+        <v>354568.5</v>
+      </c>
+      <c r="P6">
+        <v>11450.35</v>
+      </c>
+      <c r="Q6">
+        <v>263180</v>
+      </c>
+      <c r="R6">
+        <v>448609</v>
+      </c>
+      <c r="S6">
+        <v>65465</v>
+      </c>
+      <c r="T6">
+        <v>882367.99999999988</v>
+      </c>
+      <c r="U6">
+        <v>43162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2203,398 +2254,314 @@
       <c r="D7" s="1">
         <v>11025</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="G7">
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>84206.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>667194.74999999988</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>354568.5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <f>HLOOKUP(J4,Table10[[1]:[15]],3,0)</f>
+        <v>427968</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <f>MATCH(G5,G5:U5,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" t="str">
+        <f>INDEX(Table1[[Description]:[TotalPrice]],7,2)</f>
+        <v>Laptop</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>11450.35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11">
+        <f>HLOOKUP(H4,Table10[[1]:[15]],3,1)</f>
+        <v>436186</v>
+      </c>
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <f>MATCH(O5,G5:U5,0)</f>
+        <v>2</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" t="str">
+        <f>INDEX(Table1[[Description]:[TotalPrice]],10,1)</f>
+        <v>Vivo</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>263180</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <f>HLOOKUP(O4,Table10[[1]:[15]],3,0)</f>
+        <v>354568.5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12">
+        <f>MATCH(S5,G5:U5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <f>INDEX(Table1[[Description]:[TotalPrice]],13,3)</f>
+        <v>65465</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>448609</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <f>HLOOKUP(R4,Table10[[1]:[15]],3,0)</f>
+        <v>448609</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <f>MATCH(J5,G5:U5,0)</f>
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <f>INDEX(Table1[[Description]:[TotalPrice]],2,3)</f>
+        <v>436186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1">
+        <v>65465</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <f>HLOOKUP(U4,Table10[[1]:[15]],3,0)</f>
+        <v>43162</v>
+      </c>
+      <c r="I14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <f>MATCH(N5,G5:U5,0)</f>
+        <v>8</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="str">
+        <f>INDEX(Table1[[Description]:[TotalPrice]],7,1)</f>
+        <v>HP</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>882367.99999999988</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <f>HLOOKUP(S4,Table10[[1]:[15]],3,1)</f>
+        <v>43162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>43162</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
         <f>VLOOKUP(B3,Table1[[Description]:[TotalPrice]],3,0)</f>
         <v>436186</v>
       </c>
-      <c r="J7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>2</v>
-      </c>
-      <c r="R7" t="s">
-        <v>4</v>
-      </c>
-      <c r="S7" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" t="s">
-        <v>5</v>
-      </c>
-      <c r="V7" t="s">
-        <v>2</v>
-      </c>
-      <c r="W7" t="s">
-        <v>16</v>
-      </c>
-      <c r="X7" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>84206.1</v>
-      </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="C22">
         <f>VLOOKUP(B10,Table1[[Description]:[TotalPrice]],3,0)</f>
         <v>354568.5</v>
       </c>
-      <c r="J8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>229040</v>
-      </c>
-      <c r="L8">
-        <v>436186</v>
-      </c>
-      <c r="M8">
-        <v>229040</v>
-      </c>
-      <c r="N8">
-        <v>427968</v>
-      </c>
-      <c r="O8">
-        <v>65465</v>
-      </c>
-      <c r="P8">
-        <v>11025</v>
-      </c>
-      <c r="Q8">
-        <v>84206.1</v>
-      </c>
-      <c r="R8">
-        <v>667194.74999999988</v>
-      </c>
-      <c r="S8">
-        <v>354568.5</v>
-      </c>
-      <c r="T8">
-        <v>11450.35</v>
-      </c>
-      <c r="U8">
-        <v>263180</v>
-      </c>
-      <c r="V8">
-        <v>448609</v>
-      </c>
-      <c r="W8">
-        <v>65465</v>
-      </c>
-      <c r="X8">
-        <v>882367.99999999988</v>
-      </c>
-      <c r="Y8">
-        <v>43162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>667194.74999999988</v>
-      </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
+      <c r="C23">
         <f>VLOOKUP(B13,Table1[[Description]:[TotalPrice]],3,0)</f>
         <v>448609</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
-        <v>354568.5</v>
-      </c>
-      <c r="F10" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="G10">
+      <c r="C24">
         <f>VLOOKUP(B16,Table1[[Description]:[TotalPrice]],3,0)</f>
         <v>43162</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>11450.35</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
+      <c r="C25">
         <f>VLOOKUP(B14,Table1[[Description]:[TotalPrice]],3,0)</f>
         <v>65465</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1">
-        <v>263180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>448609</v>
-      </c>
-      <c r="K13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1">
-        <v>65465</v>
-      </c>
-      <c r="K14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14">
-        <f>HLOOKUP(N6,Table10[[1]:[15]],3,0)</f>
-        <v>427968</v>
-      </c>
-      <c r="N14" t="s">
-        <v>2</v>
-      </c>
-      <c r="O14">
-        <f>MATCH(K7,K7:Y7,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>43</v>
-      </c>
-      <c r="R14" t="str">
-        <f>INDEX(Table1[[Description]:[TotalPrice]],7,2)</f>
-        <v>Laptop</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
-        <v>882367.99999999988</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L15">
-        <f>HLOOKUP(L6,Table10[[1]:[15]],3,1)</f>
-        <v>436186</v>
-      </c>
-      <c r="N15" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15">
-        <f>MATCH(S7,K7:Y7,0)</f>
-        <v>2</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>44</v>
-      </c>
-      <c r="R15" t="str">
-        <f>INDEX(Table1[[Description]:[TotalPrice]],10,1)</f>
-        <v>Vivo</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1">
-        <v>43162</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16">
-        <f>HLOOKUP(S6,Table10[[1]:[15]],3,0)</f>
-        <v>354568.5</v>
-      </c>
-      <c r="N16" t="s">
-        <v>16</v>
-      </c>
-      <c r="O16">
-        <f>MATCH(W7,K7:Y7,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>45</v>
-      </c>
-      <c r="R16">
-        <f>INDEX(Table1[[Description]:[TotalPrice]],13,3)</f>
-        <v>65465</v>
-      </c>
-    </row>
-    <row r="17" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17">
-        <f>HLOOKUP(V6,Table10[[1]:[15]],3,0)</f>
-        <v>448609</v>
-      </c>
-      <c r="N17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O17">
-        <f>MATCH(N7,K7:Y7,0)</f>
-        <v>4</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>46</v>
-      </c>
-      <c r="R17">
-        <f>INDEX(Table1[[Description]:[TotalPrice]],2,3)</f>
-        <v>436186</v>
-      </c>
-    </row>
-    <row r="18" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18">
-        <f>HLOOKUP(Y6,Table10[[1]:[15]],3,0)</f>
-        <v>43162</v>
-      </c>
-      <c r="N18" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18">
-        <f>MATCH(R7,K7:Y7,0)</f>
-        <v>8</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" t="str">
-        <f>INDEX(Table1[[Description]:[TotalPrice]],7,1)</f>
-        <v>HP</v>
-      </c>
-    </row>
-    <row r="19" spans="11:18" x14ac:dyDescent="0.25">
-      <c r="K19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <f>HLOOKUP(W6,Table10[[1]:[15]],3,1)</f>
-        <v>43162</v>
       </c>
     </row>
   </sheetData>
